--- a/docs/SIMULACAO_PRECOS_ZELA.xlsx
+++ b/docs/SIMULACAO_PRECOS_ZELA.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="19">
